--- a/output_data/Nucleotide_comp_codons.xlsx
+++ b/output_data/Nucleotide_comp_codons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/PortableSSD/GitHub/rabies-codon-bias/output_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72440FB7-7ABB-7747-86A5-DDBDC2D2CA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5407F3B-47B1-8D42-933E-53AAF0E3768F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{698B2707-9161-F044-A54B-C5AB15C46DF5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>SEQUENCES \ PARAMETERS</t>
   </si>
@@ -333,16 +333,29 @@
   </si>
   <si>
     <t>G_GGC</t>
+  </si>
+  <si>
+    <t>G_GGG</t>
+  </si>
+  <si>
+    <t>G_GGA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -368,8 +381,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3425E4-3163-5249-A430-5FA79690FEDE}">
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.2">
@@ -8128,6 +8142,262 @@
         <v>100</v>
       </c>
       <c r="AP58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59">
+        <v>33.333333333333002</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>66.666666666666998</v>
+      </c>
+      <c r="F59">
+        <v>66.666666666666998</v>
+      </c>
+      <c r="G59">
+        <v>100</v>
+      </c>
+      <c r="H59" s="1">
+        <v>66.666666699999993</v>
+      </c>
+      <c r="I59">
+        <v>33.333333333333002</v>
+      </c>
+      <c r="J59">
+        <v>33.333333333333002</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>100</v>
+      </c>
+      <c r="P59">
+        <v>100</v>
+      </c>
+      <c r="Q59">
+        <v>100</v>
+      </c>
+      <c r="R59">
+        <v>100</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>100</v>
+      </c>
+      <c r="Z59">
+        <v>100</v>
+      </c>
+      <c r="AA59">
+        <v>100</v>
+      </c>
+      <c r="AB59">
+        <v>100</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>100</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59">
+        <v>0</v>
+      </c>
+      <c r="AI59">
+        <v>0</v>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>100</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>100</v>
+      </c>
+      <c r="AN59">
+        <v>100</v>
+      </c>
+      <c r="AO59">
+        <v>0</v>
+      </c>
+      <c r="AP59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>100</v>
+      </c>
+      <c r="F60">
+        <v>100</v>
+      </c>
+      <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="H60">
+        <v>100</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>100</v>
+      </c>
+      <c r="P60">
+        <v>100</v>
+      </c>
+      <c r="Q60">
+        <v>100</v>
+      </c>
+      <c r="R60">
+        <v>100</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>100</v>
+      </c>
+      <c r="Z60">
+        <v>100</v>
+      </c>
+      <c r="AA60">
+        <v>100</v>
+      </c>
+      <c r="AB60">
+        <v>100</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60">
+        <v>0</v>
+      </c>
+      <c r="AI60">
+        <v>100</v>
+      </c>
+      <c r="AJ60">
+        <v>100</v>
+      </c>
+      <c r="AK60">
+        <v>100</v>
+      </c>
+      <c r="AL60">
+        <v>100</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
+        <v>0</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
         <v>100</v>
       </c>
     </row>
